--- a/data/roster_past.xlsx
+++ b/data/roster_past.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\EFSPI\20_workshop\efspiworkshop\workshop\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE1EB23-FA62-49E1-9120-C9A14AA436CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A241B71-44F3-4414-ACB0-E66264FD710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2120" yWindow="180" windowWidth="18250" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="362">
   <si>
     <t>Year</t>
   </si>
@@ -1011,6 +1011,120 @@
   </si>
   <si>
     <t>Radboud UMC</t>
+  </si>
+  <si>
+    <t>Pharma</t>
+  </si>
+  <si>
+    <t>Federico Mattiello</t>
+  </si>
+  <si>
+    <t>Helle Lynggaard</t>
+  </si>
+  <si>
+    <t>Randi Gron</t>
+  </si>
+  <si>
+    <t>Tobias Mütze</t>
+  </si>
+  <si>
+    <t>Regulator Switzerland (Swissmedic)</t>
+  </si>
+  <si>
+    <t>Natalia Muehlemann</t>
+  </si>
+  <si>
+    <t>Curie.Bio</t>
+  </si>
+  <si>
+    <t>Marc Vandemeulebroecke</t>
+  </si>
+  <si>
+    <t>Armin Schueler</t>
+  </si>
+  <si>
+    <t>Antje Behring</t>
+  </si>
+  <si>
+    <t>Independent consultant</t>
+  </si>
+  <si>
+    <t>Susanne Urach</t>
+  </si>
+  <si>
+    <t>Taco Monster</t>
+  </si>
+  <si>
+    <t>Erasmus School of Health Policy &amp; Management</t>
+  </si>
+  <si>
+    <t>Dominic Magirr</t>
+  </si>
+  <si>
+    <t>Cordula Zeller</t>
+  </si>
+  <si>
+    <t>Jan Lucca Bilek</t>
+  </si>
+  <si>
+    <t>Gemeinsamer Bundesausschuss</t>
+  </si>
+  <si>
+    <t>Lars Beckmann</t>
+  </si>
+  <si>
+    <t>HTA Germany (IQWiG)</t>
+  </si>
+  <si>
+    <t>Robin Ristl</t>
+  </si>
+  <si>
+    <t>Medical University of Vienna</t>
+  </si>
+  <si>
+    <t>Anouk Neven</t>
+  </si>
+  <si>
+    <t>Evgeny Degtyarev</t>
+  </si>
+  <si>
+    <t>Juan Jose Abellan</t>
+  </si>
+  <si>
+    <t>Francesco Brizzi</t>
+  </si>
+  <si>
+    <t>Theresa Stadler</t>
+  </si>
+  <si>
+    <t>Swiss Data Science Center</t>
+  </si>
+  <si>
+    <t>Matthias Templ</t>
+  </si>
+  <si>
+    <t>Fachhochschule Nordwestschweiz</t>
+  </si>
+  <si>
+    <t>Laurent Servais</t>
+  </si>
+  <si>
+    <t>Hsin-Ju Hsieh</t>
+  </si>
+  <si>
+    <t>Thomas Ecker</t>
+  </si>
+  <si>
+    <t>Ecker &amp; Ecker</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>Susanne Clinch</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1060,6 +1174,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1375,17 +1492,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D288"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D342"/>
+  <sheetFormatPr defaultColWidth="5.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="66" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="5.42578125" style="1"/>
+    <col min="5" max="16384" width="5.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1516,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2016</v>
       </c>
@@ -1410,7 +1527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2016</v>
       </c>
@@ -1424,7 +1541,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2016</v>
       </c>
@@ -1438,7 +1555,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2016</v>
       </c>
@@ -1452,7 +1569,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2016</v>
       </c>
@@ -1466,7 +1583,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2016</v>
       </c>
@@ -1480,7 +1597,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2016</v>
       </c>
@@ -1494,7 +1611,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2016</v>
       </c>
@@ -1505,7 +1622,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2016</v>
       </c>
@@ -1519,7 +1636,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -1533,7 +1650,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2016</v>
       </c>
@@ -1547,7 +1664,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>2016</v>
       </c>
@@ -1561,7 +1678,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2016</v>
       </c>
@@ -1575,7 +1692,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2016</v>
       </c>
@@ -1589,7 +1706,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2016</v>
       </c>
@@ -1603,7 +1720,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2016</v>
       </c>
@@ -1617,7 +1734,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2016</v>
       </c>
@@ -1631,7 +1748,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2016</v>
       </c>
@@ -1645,7 +1762,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2016</v>
       </c>
@@ -1659,7 +1776,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2016</v>
       </c>
@@ -1673,7 +1790,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2016</v>
       </c>
@@ -1687,7 +1804,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2016</v>
       </c>
@@ -1701,7 +1818,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2017</v>
       </c>
@@ -1713,7 +1830,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2017</v>
       </c>
@@ -1727,7 +1844,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2017</v>
       </c>
@@ -1741,7 +1858,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2017</v>
       </c>
@@ -1755,7 +1872,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2017</v>
       </c>
@@ -1769,7 +1886,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2017</v>
       </c>
@@ -1781,7 +1898,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2017</v>
       </c>
@@ -1795,7 +1912,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2017</v>
       </c>
@@ -1809,7 +1926,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2017</v>
       </c>
@@ -1823,7 +1940,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2017</v>
       </c>
@@ -1837,7 +1954,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2017</v>
       </c>
@@ -1851,7 +1968,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2017</v>
       </c>
@@ -1865,7 +1982,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2017</v>
       </c>
@@ -1879,7 +1996,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2017</v>
       </c>
@@ -1893,7 +2010,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2017</v>
       </c>
@@ -1907,7 +2024,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2017</v>
       </c>
@@ -1921,7 +2038,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2017</v>
       </c>
@@ -1935,7 +2052,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2017</v>
       </c>
@@ -1949,7 +2066,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2017</v>
       </c>
@@ -1963,7 +2080,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2018</v>
       </c>
@@ -1975,7 +2092,7 @@
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2018</v>
       </c>
@@ -1989,7 +2106,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2018</v>
       </c>
@@ -2003,7 +2120,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2018</v>
       </c>
@@ -2017,7 +2134,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2018</v>
       </c>
@@ -2031,7 +2148,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2018</v>
       </c>
@@ -2045,7 +2162,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2018</v>
       </c>
@@ -2057,7 +2174,7 @@
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2018</v>
       </c>
@@ -2071,7 +2188,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2018</v>
       </c>
@@ -2083,7 +2200,7 @@
       </c>
       <c r="D51" s="1"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2018</v>
       </c>
@@ -2097,7 +2214,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2018</v>
       </c>
@@ -2111,7 +2228,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2018</v>
       </c>
@@ -2125,7 +2242,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2018</v>
       </c>
@@ -2139,7 +2256,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2018</v>
       </c>
@@ -2153,7 +2270,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2018</v>
       </c>
@@ -2167,7 +2284,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2018</v>
       </c>
@@ -2181,7 +2298,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2018</v>
       </c>
@@ -2195,7 +2312,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2018</v>
       </c>
@@ -2209,7 +2326,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2018</v>
       </c>
@@ -2223,7 +2340,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2018</v>
       </c>
@@ -2237,7 +2354,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2018</v>
       </c>
@@ -2251,7 +2368,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2018</v>
       </c>
@@ -2265,7 +2382,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2018</v>
       </c>
@@ -2279,7 +2396,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2018</v>
       </c>
@@ -2293,7 +2410,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2018</v>
       </c>
@@ -2307,7 +2424,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2019</v>
       </c>
@@ -2321,7 +2438,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2019</v>
       </c>
@@ -2335,7 +2452,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2019</v>
       </c>
@@ -2349,7 +2466,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2019</v>
       </c>
@@ -2363,7 +2480,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2019</v>
       </c>
@@ -2377,7 +2494,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2019</v>
       </c>
@@ -2391,7 +2508,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2019</v>
       </c>
@@ -2403,7 +2520,7 @@
       </c>
       <c r="D74" s="1"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2019</v>
       </c>
@@ -2415,7 +2532,7 @@
       </c>
       <c r="D75" s="1"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2019</v>
       </c>
@@ -2427,7 +2544,7 @@
       </c>
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2019</v>
       </c>
@@ -2441,7 +2558,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2019</v>
       </c>
@@ -2455,7 +2572,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2019</v>
       </c>
@@ -2469,7 +2586,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2019</v>
       </c>
@@ -2483,7 +2600,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2019</v>
       </c>
@@ -2497,7 +2614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2019</v>
       </c>
@@ -2511,7 +2628,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2019</v>
       </c>
@@ -2525,7 +2642,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2019</v>
       </c>
@@ -2539,7 +2656,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2019</v>
       </c>
@@ -2553,7 +2670,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2019</v>
       </c>
@@ -2567,7 +2684,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2019</v>
       </c>
@@ -2581,7 +2698,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2019</v>
       </c>
@@ -2595,7 +2712,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2019</v>
       </c>
@@ -2609,7 +2726,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2019</v>
       </c>
@@ -2623,7 +2740,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2020</v>
       </c>
@@ -2637,7 +2754,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2020</v>
       </c>
@@ -2651,7 +2768,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2020</v>
       </c>
@@ -2665,7 +2782,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2020</v>
       </c>
@@ -2679,7 +2796,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2020</v>
       </c>
@@ -2693,7 +2810,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2020</v>
       </c>
@@ -2707,7 +2824,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2020</v>
       </c>
@@ -2721,7 +2838,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2020</v>
       </c>
@@ -2735,7 +2852,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2020</v>
       </c>
@@ -2749,7 +2866,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>2020</v>
       </c>
@@ -2763,7 +2880,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>2020</v>
       </c>
@@ -2777,7 +2894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>2020</v>
       </c>
@@ -2791,7 +2908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>2020</v>
       </c>
@@ -2805,7 +2922,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>2020</v>
       </c>
@@ -2819,7 +2936,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>2020</v>
       </c>
@@ -2833,7 +2950,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>2021</v>
       </c>
@@ -2845,7 +2962,7 @@
       </c>
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>2021</v>
       </c>
@@ -2859,7 +2976,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2021</v>
       </c>
@@ -2873,7 +2990,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>2021</v>
       </c>
@@ -2887,7 +3004,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>2021</v>
       </c>
@@ -2901,7 +3018,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>2021</v>
       </c>
@@ -2915,7 +3032,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>2021</v>
       </c>
@@ -2929,7 +3046,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>2021</v>
       </c>
@@ -2943,7 +3060,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>2021</v>
       </c>
@@ -2957,7 +3074,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>2021</v>
       </c>
@@ -2971,7 +3088,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>2021</v>
       </c>
@@ -2983,7 +3100,7 @@
       </c>
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>2021</v>
       </c>
@@ -2995,7 +3112,7 @@
       </c>
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>2021</v>
       </c>
@@ -3006,7 +3123,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>2021</v>
       </c>
@@ -3017,7 +3134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>2021</v>
       </c>
@@ -3031,7 +3148,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>2021</v>
       </c>
@@ -3045,7 +3162,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>2021</v>
       </c>
@@ -3059,7 +3176,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>2021</v>
       </c>
@@ -3073,7 +3190,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>2021</v>
       </c>
@@ -3087,7 +3204,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>2021</v>
       </c>
@@ -3101,7 +3218,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>2021</v>
       </c>
@@ -3115,7 +3232,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>2021</v>
       </c>
@@ -3129,7 +3246,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>2021</v>
       </c>
@@ -3143,7 +3260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>2021</v>
       </c>
@@ -3157,7 +3274,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>2021</v>
       </c>
@@ -3171,7 +3288,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>2021</v>
       </c>
@@ -3185,7 +3302,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>2021</v>
       </c>
@@ -3199,7 +3316,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>2021</v>
       </c>
@@ -3213,7 +3330,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>2022</v>
       </c>
@@ -3224,7 +3341,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>2022</v>
       </c>
@@ -3235,7 +3352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>2022</v>
       </c>
@@ -3246,7 +3363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>2022</v>
       </c>
@@ -3260,7 +3377,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>2022</v>
       </c>
@@ -3274,7 +3391,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>2022</v>
       </c>
@@ -3288,7 +3405,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>2022</v>
       </c>
@@ -3302,7 +3419,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>2022</v>
       </c>
@@ -3316,7 +3433,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>2022</v>
       </c>
@@ -3330,7 +3447,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>2022</v>
       </c>
@@ -3344,7 +3461,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>2022</v>
       </c>
@@ -3358,7 +3475,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>2022</v>
       </c>
@@ -3372,7 +3489,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2022</v>
       </c>
@@ -3386,7 +3503,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>2022</v>
       </c>
@@ -3397,7 +3514,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>2022</v>
       </c>
@@ -3408,7 +3525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>2022</v>
       </c>
@@ -3419,7 +3536,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>2022</v>
       </c>
@@ -3430,7 +3547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>2022</v>
       </c>
@@ -3444,7 +3561,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>2022</v>
       </c>
@@ -3458,7 +3575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>2022</v>
       </c>
@@ -3472,7 +3589,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>2022</v>
       </c>
@@ -3486,7 +3603,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2022</v>
       </c>
@@ -3500,7 +3617,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>2022</v>
       </c>
@@ -3514,7 +3631,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>2022</v>
       </c>
@@ -3528,7 +3645,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>2022</v>
       </c>
@@ -3542,7 +3659,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>2022</v>
       </c>
@@ -3556,7 +3673,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>2022</v>
       </c>
@@ -3570,7 +3687,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>2022</v>
       </c>
@@ -3584,7 +3701,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>2022</v>
       </c>
@@ -3598,7 +3715,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>2022</v>
       </c>
@@ -3612,7 +3729,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>2023</v>
       </c>
@@ -3623,7 +3740,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>2023</v>
       </c>
@@ -3634,7 +3751,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>2023</v>
       </c>
@@ -3645,7 +3762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>2023</v>
       </c>
@@ -3659,7 +3776,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>2023</v>
       </c>
@@ -3673,7 +3790,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>2023</v>
       </c>
@@ -3687,7 +3804,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>2023</v>
       </c>
@@ -3701,7 +3818,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>2023</v>
       </c>
@@ -3715,7 +3832,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>2023</v>
       </c>
@@ -3729,7 +3846,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>2023</v>
       </c>
@@ -3743,7 +3860,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>2023</v>
       </c>
@@ -3757,7 +3874,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>2023</v>
       </c>
@@ -3771,7 +3888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>2023</v>
       </c>
@@ -3785,7 +3902,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>2023</v>
       </c>
@@ -3796,7 +3913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>2023</v>
       </c>
@@ -3810,7 +3927,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>2023</v>
       </c>
@@ -3824,7 +3941,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>2023</v>
       </c>
@@ -3838,7 +3955,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>2023</v>
       </c>
@@ -3852,7 +3969,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>2023</v>
       </c>
@@ -3866,7 +3983,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>2023</v>
       </c>
@@ -3880,7 +3997,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>2023</v>
       </c>
@@ -3894,7 +4011,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>2023</v>
       </c>
@@ -3908,7 +4025,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>2023</v>
       </c>
@@ -3922,8 +4039,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="4">
         <v>2024</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -3936,8 +4053,8 @@
         <v>209</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="4">
         <v>2024</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -3950,8 +4067,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="4">
         <v>2024</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -3964,8 +4081,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="4">
         <v>2024</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -3978,8 +4095,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="4">
         <v>2024</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -3992,8 +4109,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="4">
         <v>2024</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -4006,8 +4123,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="4">
         <v>2024</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -4020,8 +4137,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="4">
         <v>2024</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -4034,8 +4151,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="4">
         <v>2024</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -4048,8 +4165,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="4">
         <v>2024</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -4062,8 +4179,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="4">
         <v>2024</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -4076,8 +4193,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="4">
         <v>2024</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -4090,8 +4207,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="4">
         <v>2024</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -4104,8 +4221,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="4">
         <v>2024</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -4118,8 +4235,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="4">
         <v>2024</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -4132,8 +4249,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="4">
         <v>2024</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -4146,8 +4263,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="4">
         <v>2024</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -4160,8 +4277,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="4">
         <v>2024</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -4174,8 +4291,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="4">
         <v>2024</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -4188,8 +4305,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="4">
         <v>2024</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -4202,8 +4319,8 @@
         <v>234</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="4">
         <v>2024</v>
       </c>
       <c r="B207" s="2" t="s">
@@ -4216,8 +4333,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="4">
         <v>2024</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -4230,8 +4347,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="4">
         <v>2024</v>
       </c>
       <c r="B209" s="2" t="s">
@@ -4244,8 +4361,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="4">
         <v>2024</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -4258,8 +4375,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="4">
         <v>2024</v>
       </c>
       <c r="B211" s="2" t="s">
@@ -4272,8 +4389,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="4">
         <v>2024</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -4286,8 +4403,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="4">
         <v>2024</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -4300,8 +4417,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="4">
         <v>2024</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -4314,8 +4431,8 @@
         <v>234</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="4">
         <v>2024</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -4328,8 +4445,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="4">
         <v>2024</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -4342,8 +4459,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="4">
         <v>2024</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -4356,8 +4473,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="4">
         <v>2024</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -4370,8 +4487,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="4">
         <v>2024</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -4384,8 +4501,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" s="4">
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -4398,8 +4515,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="4">
         <v>2024</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -4412,8 +4529,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="4">
         <v>2024</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -4426,8 +4543,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="4">
         <v>2024</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -4440,8 +4557,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="4">
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -4454,8 +4571,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="4">
         <v>2024</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -4468,8 +4585,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="4">
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -4482,8 +4599,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="4">
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="s">
@@ -4496,8 +4613,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="4">
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -4510,8 +4627,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="4">
         <v>2024</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -4524,8 +4641,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="4">
         <v>2024</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -4538,8 +4655,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="4">
         <v>2024</v>
       </c>
       <c r="B231" s="2" t="s">
@@ -4552,8 +4669,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="4">
         <v>2024</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -4566,8 +4683,8 @@
         <v>264</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="4">
         <v>2024</v>
       </c>
       <c r="B233" s="2" t="s">
@@ -4580,8 +4697,8 @@
         <v>264</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="4">
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -4594,8 +4711,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="4">
         <v>2024</v>
       </c>
       <c r="B235" s="2" t="s">
@@ -4608,7 +4725,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>2025</v>
       </c>
@@ -4622,7 +4739,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>2025</v>
       </c>
@@ -4636,7 +4753,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2025</v>
       </c>
@@ -4650,7 +4767,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>2025</v>
       </c>
@@ -4664,7 +4781,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>2025</v>
       </c>
@@ -4678,7 +4795,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>2025</v>
       </c>
@@ -4692,7 +4809,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2025</v>
       </c>
@@ -4706,7 +4823,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>2025</v>
       </c>
@@ -4720,7 +4837,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>2025</v>
       </c>
@@ -4734,7 +4851,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>2025</v>
       </c>
@@ -4748,7 +4865,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2025</v>
       </c>
@@ -4762,7 +4879,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>2025</v>
       </c>
@@ -4776,7 +4893,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>2025</v>
       </c>
@@ -4790,7 +4907,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>2025</v>
       </c>
@@ -4804,7 +4921,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2025</v>
       </c>
@@ -4818,7 +4935,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>2025</v>
       </c>
@@ -4832,7 +4949,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>2025</v>
       </c>
@@ -4846,7 +4963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>2025</v>
       </c>
@@ -4860,7 +4977,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2025</v>
       </c>
@@ -4874,7 +4991,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>2025</v>
       </c>
@@ -4888,7 +5005,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>2025</v>
       </c>
@@ -4902,7 +5019,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>2025</v>
       </c>
@@ -4916,7 +5033,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2025</v>
       </c>
@@ -4930,7 +5047,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>2025</v>
       </c>
@@ -4944,7 +5061,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>2025</v>
       </c>
@@ -4958,7 +5075,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>2025</v>
       </c>
@@ -4972,7 +5089,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2025</v>
       </c>
@@ -4986,7 +5103,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>2025</v>
       </c>
@@ -5000,7 +5117,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>2025</v>
       </c>
@@ -5014,7 +5131,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>2025</v>
       </c>
@@ -5028,7 +5145,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2025</v>
       </c>
@@ -5042,7 +5159,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>2025</v>
       </c>
@@ -5056,7 +5173,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>2025</v>
       </c>
@@ -5070,7 +5187,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>2025</v>
       </c>
@@ -5084,7 +5201,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2025</v>
       </c>
@@ -5098,7 +5215,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>2025</v>
       </c>
@@ -5112,7 +5229,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>2025</v>
       </c>
@@ -5126,7 +5243,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>2025</v>
       </c>
@@ -5140,7 +5257,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2025</v>
       </c>
@@ -5154,7 +5271,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>2025</v>
       </c>
@@ -5168,7 +5285,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>2025</v>
       </c>
@@ -5182,7 +5299,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>2025</v>
       </c>
@@ -5196,7 +5313,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2025</v>
       </c>
@@ -5210,7 +5327,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>2025</v>
       </c>
@@ -5224,7 +5341,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>2025</v>
       </c>
@@ -5238,7 +5355,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>2025</v>
       </c>
@@ -5252,7 +5369,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2025</v>
       </c>
@@ -5266,7 +5383,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>2025</v>
       </c>
@@ -5280,7 +5397,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>2025</v>
       </c>
@@ -5294,7 +5411,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>2025</v>
       </c>
@@ -5308,7 +5425,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2025</v>
       </c>
@@ -5322,7 +5439,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>2025</v>
       </c>
@@ -5336,7 +5453,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>2025</v>
       </c>
@@ -5349,6 +5466,699 @@
       <c r="D288" t="s">
         <v>323</v>
       </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C289" t="s">
+        <v>285</v>
+      </c>
+      <c r="D289" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C290" t="s">
+        <v>345</v>
+      </c>
+      <c r="D290" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C291" t="s">
+        <v>23</v>
+      </c>
+      <c r="D291" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C292" t="s">
+        <v>351</v>
+      </c>
+      <c r="D292" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C293" t="s">
+        <v>353</v>
+      </c>
+      <c r="D293" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" t="s">
+        <v>334</v>
+      </c>
+      <c r="D294" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" t="s">
+        <v>341</v>
+      </c>
+      <c r="D295" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C296" t="s">
+        <v>343</v>
+      </c>
+      <c r="D296" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C297" t="s">
+        <v>357</v>
+      </c>
+      <c r="D297" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C298" t="s">
+        <v>330</v>
+      </c>
+      <c r="D298" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C299" t="s">
+        <v>355</v>
+      </c>
+      <c r="D299" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C300" t="s">
+        <v>211</v>
+      </c>
+      <c r="D300" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C301" t="s">
+        <v>289</v>
+      </c>
+      <c r="D301" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C302" t="s">
+        <v>325</v>
+      </c>
+      <c r="D302" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C303" t="s">
+        <v>326</v>
+      </c>
+      <c r="D303" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C304" t="s">
+        <v>327</v>
+      </c>
+      <c r="D304" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C305" t="s">
+        <v>217</v>
+      </c>
+      <c r="D305" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C306" t="s">
+        <v>328</v>
+      </c>
+      <c r="D306" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C307" t="s">
+        <v>226</v>
+      </c>
+      <c r="D307" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C308" t="s">
+        <v>332</v>
+      </c>
+      <c r="D308" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C309" t="s">
+        <v>339</v>
+      </c>
+      <c r="D309" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C310" t="s">
+        <v>340</v>
+      </c>
+      <c r="D310" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C311" t="s">
+        <v>214</v>
+      </c>
+      <c r="D311" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C312" t="s">
+        <v>348</v>
+      </c>
+      <c r="D312" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C313" t="s">
+        <v>302</v>
+      </c>
+      <c r="D313" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C314" t="s">
+        <v>252</v>
+      </c>
+      <c r="D314" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C315" t="s">
+        <v>250</v>
+      </c>
+      <c r="D315" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C316" t="s">
+        <v>350</v>
+      </c>
+      <c r="D316" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C317" t="s">
+        <v>356</v>
+      </c>
+      <c r="D317" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C318" t="s">
+        <v>361</v>
+      </c>
+      <c r="D318" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C319" t="s">
+        <v>258</v>
+      </c>
+      <c r="D319" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C320" t="s">
+        <v>221</v>
+      </c>
+      <c r="D320" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C321" t="s">
+        <v>53</v>
+      </c>
+      <c r="D321" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C322" t="s">
+        <v>36</v>
+      </c>
+      <c r="D322" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C323" t="s">
+        <v>319</v>
+      </c>
+      <c r="D323" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C324" t="s">
+        <v>230</v>
+      </c>
+      <c r="D324" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C325" t="s">
+        <v>236</v>
+      </c>
+      <c r="D325" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C326" t="s">
+        <v>19</v>
+      </c>
+      <c r="D326" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C327" t="s">
+        <v>218</v>
+      </c>
+      <c r="D327" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C328" t="s">
+        <v>333</v>
+      </c>
+      <c r="D328" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C329" t="s">
+        <v>336</v>
+      </c>
+      <c r="D329" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C330" t="s">
+        <v>337</v>
+      </c>
+      <c r="D330" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C331" t="s">
+        <v>10</v>
+      </c>
+      <c r="D331" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C332" t="s">
+        <v>347</v>
+      </c>
+      <c r="D332" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C333" t="s">
+        <v>349</v>
+      </c>
+      <c r="D333" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C334" t="s">
+        <v>47</v>
+      </c>
+      <c r="D334" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C335" t="s">
+        <v>311</v>
+      </c>
+      <c r="D335" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="4"/>
+      <c r="B336" s="4"/>
+      <c r="C336"/>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4"/>
+      <c r="B337" s="4"/>
+      <c r="C337"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4"/>
+      <c r="B338" s="4"/>
+      <c r="C338"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="4"/>
+      <c r="B339" s="4"/>
+      <c r="C339"/>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4"/>
+      <c r="B340" s="4"/>
+      <c r="C340"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="4"/>
+      <c r="B341" s="4"/>
+      <c r="C341"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4"/>
+      <c r="B342" s="4"/>
+      <c r="C342"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/roster_past.xlsx
+++ b/data/roster_past.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A241B71-44F3-4414-ACB0-E66264FD710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19797BCF-825A-48A3-B133-C3BF4FA43BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="180" windowWidth="18250" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="361">
   <si>
     <t>Year</t>
   </si>
@@ -1011,9 +1011,6 @@
   </si>
   <si>
     <t>Radboud UMC</t>
-  </si>
-  <si>
-    <t>Pharma</t>
   </si>
   <si>
     <t>Federico Mattiello</t>
@@ -5478,7 +5475,7 @@
         <v>285</v>
       </c>
       <c r="D289" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -5489,10 +5486,10 @@
         <v>17</v>
       </c>
       <c r="C290" t="s">
+        <v>344</v>
+      </c>
+      <c r="D290" t="s">
         <v>345</v>
-      </c>
-      <c r="D290" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -5517,10 +5514,10 @@
         <v>17</v>
       </c>
       <c r="C292" t="s">
+        <v>350</v>
+      </c>
+      <c r="D292" t="s">
         <v>351</v>
-      </c>
-      <c r="D292" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -5531,10 +5528,10 @@
         <v>17</v>
       </c>
       <c r="C293" t="s">
+        <v>352</v>
+      </c>
+      <c r="D293" t="s">
         <v>353</v>
-      </c>
-      <c r="D293" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -5545,10 +5542,10 @@
         <v>7</v>
       </c>
       <c r="C294" t="s">
+        <v>333</v>
+      </c>
+      <c r="D294" t="s">
         <v>334</v>
-      </c>
-      <c r="D294" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -5559,10 +5556,10 @@
         <v>7</v>
       </c>
       <c r="C295" t="s">
+        <v>340</v>
+      </c>
+      <c r="D295" t="s">
         <v>341</v>
-      </c>
-      <c r="D295" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -5573,10 +5570,10 @@
         <v>7</v>
       </c>
       <c r="C296" t="s">
+        <v>342</v>
+      </c>
+      <c r="D296" t="s">
         <v>343</v>
-      </c>
-      <c r="D296" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -5587,10 +5584,10 @@
         <v>7</v>
       </c>
       <c r="C297" t="s">
+        <v>356</v>
+      </c>
+      <c r="D297" t="s">
         <v>357</v>
-      </c>
-      <c r="D297" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -5598,13 +5595,13 @@
         <v>2026</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C298" t="s">
+        <v>329</v>
+      </c>
+      <c r="D298" t="s">
         <v>330</v>
-      </c>
-      <c r="D298" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -5615,18 +5612,18 @@
         <v>17</v>
       </c>
       <c r="C299" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D299" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>2026</v>
       </c>
-      <c r="B300" s="4" t="s">
-        <v>324</v>
+      <c r="B300" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C300" t="s">
         <v>211</v>
@@ -5639,8 +5636,8 @@
       <c r="A301" s="4">
         <v>2026</v>
       </c>
-      <c r="B301" s="4" t="s">
-        <v>324</v>
+      <c r="B301" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C301" t="s">
         <v>289</v>
@@ -5653,11 +5650,11 @@
       <c r="A302" s="4">
         <v>2026</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C302" t="s">
         <v>324</v>
-      </c>
-      <c r="C302" t="s">
-        <v>325</v>
       </c>
       <c r="D302" t="s">
         <v>68</v>
@@ -5667,11 +5664,11 @@
       <c r="A303" s="4">
         <v>2026</v>
       </c>
-      <c r="B303" s="4" t="s">
-        <v>324</v>
+      <c r="B303" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C303" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D303" t="s">
         <v>163</v>
@@ -5681,11 +5678,11 @@
       <c r="A304" s="4">
         <v>2026</v>
       </c>
-      <c r="B304" s="4" t="s">
-        <v>324</v>
+      <c r="B304" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C304" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D304" t="s">
         <v>163</v>
@@ -5695,8 +5692,8 @@
       <c r="A305" s="4">
         <v>2026</v>
       </c>
-      <c r="B305" s="4" t="s">
-        <v>324</v>
+      <c r="B305" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C305" t="s">
         <v>217</v>
@@ -5709,11 +5706,11 @@
       <c r="A306" s="4">
         <v>2026</v>
       </c>
-      <c r="B306" s="4" t="s">
-        <v>324</v>
+      <c r="B306" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C306" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D306" t="s">
         <v>67</v>
@@ -5723,8 +5720,8 @@
       <c r="A307" s="4">
         <v>2026</v>
       </c>
-      <c r="B307" s="4" t="s">
-        <v>324</v>
+      <c r="B307" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C307" t="s">
         <v>226</v>
@@ -5737,11 +5734,11 @@
       <c r="A308" s="4">
         <v>2026</v>
       </c>
-      <c r="B308" s="4" t="s">
-        <v>324</v>
+      <c r="B308" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C308" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D308" t="s">
         <v>70</v>
@@ -5751,11 +5748,11 @@
       <c r="A309" s="4">
         <v>2026</v>
       </c>
-      <c r="B309" s="4" t="s">
-        <v>324</v>
+      <c r="B309" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C309" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D309" t="s">
         <v>67</v>
@@ -5765,11 +5762,11 @@
       <c r="A310" s="4">
         <v>2026</v>
       </c>
-      <c r="B310" s="4" t="s">
-        <v>324</v>
+      <c r="B310" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C310" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D310" t="s">
         <v>290</v>
@@ -5779,8 +5776,8 @@
       <c r="A311" s="4">
         <v>2026</v>
       </c>
-      <c r="B311" s="4" t="s">
-        <v>324</v>
+      <c r="B311" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C311" t="s">
         <v>214</v>
@@ -5793,11 +5790,11 @@
       <c r="A312" s="4">
         <v>2026</v>
       </c>
-      <c r="B312" s="4" t="s">
-        <v>324</v>
+      <c r="B312" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C312" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D312" t="s">
         <v>67</v>
@@ -5807,8 +5804,8 @@
       <c r="A313" s="4">
         <v>2026</v>
       </c>
-      <c r="B313" s="4" t="s">
-        <v>324</v>
+      <c r="B313" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C313" t="s">
         <v>302</v>
@@ -5821,8 +5818,8 @@
       <c r="A314" s="4">
         <v>2026</v>
       </c>
-      <c r="B314" s="4" t="s">
-        <v>324</v>
+      <c r="B314" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C314" t="s">
         <v>252</v>
@@ -5835,8 +5832,8 @@
       <c r="A315" s="4">
         <v>2026</v>
       </c>
-      <c r="B315" s="4" t="s">
-        <v>324</v>
+      <c r="B315" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C315" t="s">
         <v>250</v>
@@ -5849,11 +5846,11 @@
       <c r="A316" s="4">
         <v>2026</v>
       </c>
-      <c r="B316" s="4" t="s">
-        <v>324</v>
+      <c r="B316" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C316" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D316" t="s">
         <v>68</v>
@@ -5863,11 +5860,11 @@
       <c r="A317" s="4">
         <v>2026</v>
       </c>
-      <c r="B317" s="4" t="s">
-        <v>324</v>
+      <c r="B317" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C317" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D317" t="s">
         <v>227</v>
@@ -5877,11 +5874,11 @@
       <c r="A318" s="4">
         <v>2026</v>
       </c>
-      <c r="B318" s="4" t="s">
-        <v>324</v>
+      <c r="B318" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C318" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D318" t="s">
         <v>68</v>
@@ -5954,7 +5951,7 @@
         <v>319</v>
       </c>
       <c r="D323" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6021,7 +6018,7 @@
         <v>190</v>
       </c>
       <c r="C328" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D328" t="s">
         <v>223</v>
@@ -6035,7 +6032,7 @@
         <v>190</v>
       </c>
       <c r="C329" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D329" t="s">
         <v>239</v>
@@ -6049,7 +6046,7 @@
         <v>190</v>
       </c>
       <c r="C330" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D330" t="s">
         <v>222</v>
@@ -6077,7 +6074,7 @@
         <v>190</v>
       </c>
       <c r="C332" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D332" t="s">
         <v>216</v>
@@ -6091,7 +6088,7 @@
         <v>190</v>
       </c>
       <c r="C333" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D333" t="s">
         <v>216</v>
